--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי ימין - מסתובב ברחובות</v>
+        <v>חג׳בי - כלה בלבן קאבר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410584&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410601&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-23</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי ימין - מסתובב ברחובות</v>
+        <v>חג׳בי - כלה בלבן קאבר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רגב קהלני - כוסות של יין אדום</v>
+        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410583&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410600&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-23</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רגב קהלני - כוסות של יין אדום</v>
+        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>קיזל - אמת חיי</v>
+        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410582&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410599&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-23</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>קיזל - אמת חיי</v>
+        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מיכאל יגודאייב - הנעליים שנשארו</v>
+        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410579&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410598&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-23</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מיכאל יגודאייב - הנעליים שנשארו</v>
+        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליאור קקון &amp; שקד סולומון - שבועה באוקטובר</v>
+        <v>שיראל חדד - יאללה תרקדו</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410578&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410597&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D6" t="str">
         <v>2026-04-23</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליאור קקון &amp; שקד סולומון - שבועה באוקטובר</v>
+        <v>שיראל חדד - יאללה תרקדו</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>להקת פיקוד דרום &amp; חני נחמיאס &amp; אביבה אבידן - פרחים בקנה 2026</v>
+        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410577&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410596&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D7" t="str">
         <v>2026-04-23</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>להקת פיקוד דרום &amp; חני נחמיאס &amp; אביבה אבידן - פרחים בקנה 2026</v>
+        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>טלי רבקה סימן טוב - חזרתי 2026</v>
+        <v>פרחי ירושלים - ישראל שלי</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410576&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410595&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D8" t="str">
         <v>2026-04-23</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>טלי רבקה סימן טוב - חזרתי 2026</v>
+        <v>פרחי ירושלים - ישראל שלי</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>זיו אלול - קום לביא</v>
+        <v>עילאי פרץ - אהבה משולשת</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410575&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410594&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D9" t="str">
         <v>2026-04-23</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>זיו אלול - קום לביא</v>
+        <v>עילאי פרץ - אהבה משולשת</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אייל אלבז - שיר ליואב</v>
+        <v>מלכה בי &amp; דותנס - אני יכול</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410574&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410593&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D10" t="str">
         <v>2026-04-23</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אייל אלבז - שיר ליואב</v>
+        <v>מלכה בי &amp; דותנס - אני יכול</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אבי אילסון - בזכותם - גרסה ווקאלית</v>
+        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410573&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410592&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D11" t="str">
         <v>2026-04-23</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אבי אילסון - בזכותם - גרסה ווקאלית</v>
+        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>האחים בכר - נשאר הגעגוע - גרסה ווקאלית</v>
+        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410572&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410591&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D12" t="str">
         <v>2026-04-23</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>האחים בכר - נשאר הגעגוע - גרסה ווקאלית</v>
+        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>אליה לוי - אהבת השם</v>
+        <v>אריאל קנדאבי - מצאתי מקום</v>
       </c>
       <c r="B13" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410571&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410590&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D13" t="str">
         <v>2026-04-23</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>אליה לוי - אהבת השם</v>
+        <v>אריאל קנדאבי - מצאתי מקום</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>אליאור מדר - שלוש מילים קטנות</v>
+        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
       </c>
       <c r="B14" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410570&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410589&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D14" t="str">
         <v>2026-04-23</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>אליאור מדר - שלוש מילים קטנות</v>
+        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>אבי אילסון &amp; מוטי איידנסון - דיבור של הלב - גרסה ווקאלית</v>
+        <v>איתיאל - מחרוזת דמעות 2026</v>
       </c>
       <c r="B15" t="str">
-        <v>2026-04-22</v>
+        <v>2026-04-23</v>
       </c>
       <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410569&amp;sid=33c8f201f01b74fadaa78a8b9e3d1538</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410588&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D15" t="str">
         <v>2026-04-23</v>
@@ -963,12 +963,50 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>אבי אילסון &amp; מוטי איידנסון - דיבור של הלב - גרסה ווקאלית</v>
+        <v>איתיאל - מחרוזת דמעות 2026</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אבנתא דליבא - האור הטוב הזה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410587&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אבנתא דליבא - האור הטוב הזה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חג׳בי - כלה בלבן קאבר</v>
+        <v>יובל גולד - בית במושב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410601&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410610&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חג׳בי - כלה בלבן קאבר</v>
+        <v>יובל גולד - בית במושב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
+        <v>מיטב אמני ישראל - אשת חיל 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410600&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410609&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
+        <v>מיטב אמני ישראל - אשת חיל 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
+        <v>נאור כהן - לא לבד</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410599&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410608&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
+        <v>נאור כהן - לא לבד</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
+        <v>מורן לוי - מי אמור</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410598&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410607&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,430 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>שיראל חדד - יאללה תרקדו</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410597&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>שיראל חדד - יאללה תרקדו</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410596&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>פרחי ירושלים - ישראל שלי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410595&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>פרחי ירושלים - ישראל שלי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>עילאי פרץ - אהבה משולשת</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410594&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>עילאי פרץ - אהבה משולשת</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>מלכה בי &amp; דותנס - אני יכול</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410593&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>מלכה בי &amp; דותנס - אני יכול</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410592&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410591&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אריאל קנדאבי - מצאתי מקום</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410590&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אריאל קנדאבי - מצאתי מקום</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410589&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>איתיאל - מחרוזת דמעות 2026</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410588&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>איתיאל - מחרוזת דמעות 2026</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אבנתא דליבא - האור הטוב הזה</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410587&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אבנתא דליבא - האור הטוב הזה</v>
+        <v>מורן לוי - מי אמור</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל גולד - בית במושב</v>
+        <v>תהילה - מה שאני</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410610&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410612&amp;sid=14abf7149976c01670080bda4e258547</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-24</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל גולד - בית במושב</v>
+        <v>תהילה - מה שאני</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מיטב אמני ישראל - אשת חיל 2026</v>
+        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410609&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410611&amp;sid=14abf7149976c01670080bda4e258547</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-24</v>
@@ -507,88 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מיטב אמני ישראל - אשת חיל 2026</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נאור כהן - לא לבד</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410608&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נאור כהן - לא לבד</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מורן לוי - מי אמור</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410607&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מורן לוי - מי אמור</v>
+        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תהילה - מה שאני</v>
+        <v>אמיר חיים - את כל רגע משתנה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410612&amp;sid=14abf7149976c01670080bda4e258547</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410618&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תהילה - מה שאני</v>
+        <v>אמיר חיים - את כל רגע משתנה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
+        <v>אורן כהן - בסוף הכל נגמר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410611&amp;sid=14abf7149976c01670080bda4e258547</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410617&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,12 +507,88 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
+        <v>אורן כהן - בסוף הכל נגמר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אבנר הררי - הזאב האחרון</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410616&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אבנר הררי - הזאב האחרון</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אביגיל - אני רק ילדה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410615&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אביגיל - אני רק ילדה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אמיר חיים - את כל רגע משתנה</v>
+        <v>ויולט - בסוף יגיע הבוקר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410618&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410621&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-26</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אמיר חיים - את כל רגע משתנה</v>
+        <v>ויולט - בסוף יגיע הבוקר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אורן כהן - בסוף הכל נגמר</v>
+        <v>היוצר האלמוני - איך ממשיכים מכאן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410617&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410620&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-26</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אורן כהן - בסוף הכל נגמר</v>
+        <v>היוצר האלמוני - איך ממשיכים מכאן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אבנר הררי - הזאב האחרון</v>
+        <v>אסאלה - אהבה לחיילים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410616&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410619&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-26</v>
@@ -545,50 +545,12 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אבנר הררי - הזאב האחרון</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>אביגיל - אני רק ילדה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410615&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>אביגיל - אני רק ילדה</v>
+        <v>אסאלה - אהבה לחיילים</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ויולט - בסוף יגיע הבוקר</v>
+        <v>שקד אבידר - רגע לנשום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410621&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410626&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-26</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ויולט - בסוף יגיע הבוקר</v>
+        <v>שקד אבידר - רגע לנשום</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>היוצר האלמוני - איך ממשיכים מכאן</v>
+        <v>שי וינר - יבוא שלום - גרסה ווקאלית</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410620&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410625&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-26</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>היוצר האלמוני - איך ממשיכים מכאן</v>
+        <v>שי וינר - יבוא שלום - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אסאלה - אהבה לחיילים</v>
+        <v>מלי יקותיאל - אדע לאהוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410619&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410624&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-26</v>
@@ -545,12 +545,88 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אסאלה - אהבה לחיילים</v>
+        <v>מלי יקותיאל - אדע לאהוב</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מאור גוילי - שורף אדומים</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410623&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מאור גוילי - שורף אדומים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>יוסף עבאדי - רגעים של אושר - גרסה ווקאלית</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410622&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>יוסף עבאדי - רגעים של אושר - גרסה ווקאלית</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/mizrahit/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שקד אבידר - רגע לנשום</v>
+        <v>יאיר רינגר &amp; שיר רינגר - מזיז את הגוף</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410626&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410634&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שקד אבידר - רגע לנשום</v>
+        <v>יאיר רינגר &amp; שיר רינגר - מזיז את הגוף</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שי וינר - יבוא שלום - גרסה ווקאלית</v>
+        <v>תומר קינן - חלום במציאות</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410625&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410633&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שי וינר - יבוא שלום - גרסה ווקאלית</v>
+        <v>תומר קינן - חלום במציאות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>מלי יקותיאל - אדע לאהוב</v>
+        <v>שלומי ימין - אוהב אותך</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410624&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410632&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>מלי יקותיאל - אדע לאהוב</v>
+        <v>שלומי ימין - אוהב אותך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מאור גוילי - שורף אדומים</v>
+        <v>שיראל חדד - אמא שלה</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410623&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410631&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מאור גוילי - שורף אדומים</v>
+        <v>שיראל חדד - אמא שלה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>יוסף עבאדי - רגעים של אושר - גרסה ווקאלית</v>
+        <v>אניס נקש - בליבי</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410622&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410629&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,12 +621,50 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>יוסף עבאדי - רגעים של אושר - גרסה ווקאלית</v>
+        <v>אניס נקש - בליבי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אברהם טל &amp; מוש בן ארי - מה אם הייתי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410628&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אברהם טל &amp; מוש בן ארי - מה אם הייתי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>